--- a/Nakit Dengesi.xlsx
+++ b/Nakit Dengesi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/omerozogul/Desktop/DashboardProje/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\splktfs\Aktif Pasif Yonetimi\Aktif Pasif\PARA PİYASALARI\Reports\APKO\APKO Veriler\github_excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18435E31-7979-824B-89DE-E6B53FB93563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF96C3BD-07FA-4900-93B2-CDDECD4DFF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16080" tabRatio="810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28710" yWindow="-16440" windowWidth="29040" windowHeight="15720" tabRatio="810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veri_Aylık" sheetId="9" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="6">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -70,7 +70,7 @@
     <numFmt numFmtId="166" formatCode="#."/>
     <numFmt numFmtId="167" formatCode="mmm"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -324,9 +324,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -364,7 +364,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -470,7 +470,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -612,7 +612,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -621,17 +621,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E73"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="11"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.83203125" style="3"/>
+    <col min="4" max="4" width="15.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.77734375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -648,7 +648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>44196</v>
       </c>
@@ -667,7 +667,7 @@
         <v>-43763.57</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>44227</v>
       </c>
@@ -686,7 +686,7 @@
         <v>-48848.15</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>44255</v>
       </c>
@@ -705,7 +705,7 @@
         <v>-41063.17</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>44286</v>
       </c>
@@ -724,7 +724,7 @@
         <v>12528.450000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>44316</v>
       </c>
@@ -743,7 +743,7 @@
         <v>11050.010000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>44347</v>
       </c>
@@ -762,7 +762,7 @@
         <v>-7134.0599999999959</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>44377</v>
       </c>
@@ -781,7 +781,7 @@
         <v>-7691.6599999999962</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>44408</v>
       </c>
@@ -800,7 +800,7 @@
         <v>-54006.82</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>44439</v>
       </c>
@@ -819,7 +819,7 @@
         <v>22761.579999999994</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>44469</v>
       </c>
@@ -838,7 +838,7 @@
         <v>2198.2599999999948</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>44500</v>
       </c>
@@ -857,7 +857,7 @@
         <v>10091.809999999994</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>44530</v>
       </c>
@@ -876,7 +876,7 @@
         <v>53492.409999999989</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>44561</v>
       </c>
@@ -895,7 +895,7 @@
         <v>12327.440000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>44592</v>
       </c>
@@ -914,7 +914,7 @@
         <v>-7673.8199999999961</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>44620</v>
       </c>
@@ -933,7 +933,7 @@
         <v>80349.009999999995</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>44651</v>
       </c>
@@ -952,7 +952,7 @@
         <v>9569.6699999999983</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>44681</v>
       </c>
@@ -971,7 +971,7 @@
         <v>-18067.149999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>44682</v>
       </c>
@@ -990,7 +990,7 @@
         <v>164834.65999999997</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>44713</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>150636.29999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>44743</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>119190.90999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>44774</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>90012.489999999991</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>44805</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>62188.53</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>44835</v>
       </c>
@@ -1085,7 +1085,7 @@
         <v>40836.839999999982</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>44867</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>118433.36000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>44899</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>110259.99999999997</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>44931</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>100763.34</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>44963</v>
       </c>
@@ -1161,7 +1161,7 @@
         <v>-135222.79</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>44995</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>-116203.33000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>45027</v>
       </c>
@@ -1199,7 +1199,7 @@
         <v>-219313.04000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>45059</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>-118402.85000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>45091</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>-288609.17000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>45123</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>-157630.60000000003</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>45155</v>
       </c>
@@ -1275,7 +1275,7 @@
         <v>-64741.110000000015</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>45187</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>-39004.979999999989</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>45217</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>-51550.060000000034</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>45250</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>4588.7100000001083</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>45283</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>-71666.890000000043</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>45316</v>
       </c>
@@ -1370,7 +1370,7 @@
         <v>-131595.26000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>45349</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>-139071.53999999995</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>45382</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>-244673.81</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>45412</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>-244598.44999999995</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>45443</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>-172963.34000000003</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>45473</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>-322492.52999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>45504</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>-423571</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45535</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>-672604.97</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45565</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>-711854.94</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>45596</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>-729906.26</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>45626</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>-839302.26</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>45657</v>
       </c>
@@ -1579,7 +1579,7 @@
         <v>-929244.38</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>45688</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>-889322.59</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>45716</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>-1007894.4299999999</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>45747</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>-1068006.79</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>45777</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>-862778.25</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>45808</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>-851903.68000000028</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>45838</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>-724447.88000000012</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>45869</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>-622479.35000000021</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>45900</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>-264640.21000000014</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>45930</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>-336748.76</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>45961</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>-329364.01999999996</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>45991</v>
       </c>
@@ -1788,36 +1788,50 @@
         <v>-223890.91000000009</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>46022</v>
       </c>
       <c r="B62" s="2">
-        <v>-216923</v>
+        <v>-218235.67</v>
       </c>
       <c r="C62" s="2">
-        <v>333150</v>
+        <v>-333819.82</v>
       </c>
       <c r="D62" s="2">
         <f t="shared" ref="D62" si="3">SUM(C51:C62)</f>
-        <v>-1444883.23</v>
+        <v>-2111853.0499999998</v>
       </c>
       <c r="E62" s="5">
         <f t="shared" ref="E62" si="4">SUM(B51:B62)</f>
-        <v>-181514.29000000004</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="D63" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="3:5">
+        <v>-182826.96000000005</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>46053</v>
+      </c>
+      <c r="B63" s="2">
+        <v>207493.81</v>
+      </c>
+      <c r="C63" s="2">
+        <v>-246186.47</v>
+      </c>
+      <c r="D63" s="2">
+        <f t="shared" ref="D63" si="5">SUM(C52:C63)</f>
+        <v>-2153021.4900000002</v>
+      </c>
+      <c r="E63" s="5">
+        <f t="shared" ref="E63" si="6">SUM(B52:B63)</f>
+        <v>79255.92999999992</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D65" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="3:5">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C66" s="3" t="s">
         <v>0</v>
       </c>
@@ -1825,12 +1839,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="3:5">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B72" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="C72" s="3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="3:5">
+      <c r="E72" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D73" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E73" s="3" t="s">
         <v>0</v>
       </c>
@@ -1839,4 +1862,10 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{ce47449c-aead-4773-aea9-0d789a4a6973}" enabled="1" method="Privileged" siteId="{a71b8764-0a7a-4511-8f04-04867f0718ab}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>